--- a/Volunteer_Schedule.xlsx
+++ b/Volunteer_Schedule.xlsx
@@ -466,62 +466,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Taylor Liu</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>twliew@uwaterloo.ca</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Harpreet Ghotra</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>harp@uwaterloo.ca</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Taylor Liu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>twliew@uwaterloo.ca</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Taylor Liew</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>twliew@uwaterloo.ca</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Nicole Thapa</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>nicole@uwaterloo.ca</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Harpreet Ghotra</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>harp@uwaterloo.ca</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Taylor Liu</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>twliew@uwaterloo.ca</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Taylor Liew</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>twliew@uwaterloo.ca</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nicole Thapa</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nicole@uwaterloo.ca</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Nicole Thapa</t>
+          <t>Dharsaa Bhagudeva</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>nicole@uwaterloo.ca</t>
+          <t>dhar@uwaterloo.ca</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Patrick Star</t>
+          <t>Bob Smith</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>nicole@uwaterloo.ca</t>
+          <t>twliew@uwaterloo.ca</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Patrick Star</t>
+          <t>Bob Smith</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>nicole@uwaterloo.ca</t>
+          <t>twliew@uwaterloo.ca</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
